--- a/dev/StructureDefinition-bc-practitioner.xlsx
+++ b/dev/StructureDefinition-bc-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3244,7 +3244,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>136</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>160</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>165</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>170</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>175</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>180</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>185</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>190</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>195</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>200</v>
       </c>
@@ -4616,7 +4616,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>205</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>210</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>220</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>229</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>238</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>320</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>330</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>430</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>439</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>453</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>472</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>482</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>487</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>489</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>496</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>504</v>
       </c>
@@ -12980,7 +12980,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>595</v>
       </c>
@@ -13096,7 +13096,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>602</v>
       </c>
@@ -13210,7 +13210,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>609</v>
       </c>
@@ -13550,7 +13550,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>620</v>
       </c>
@@ -13664,7 +13664,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>622</v>
       </c>
@@ -13778,7 +13778,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>623</v>
       </c>
@@ -14126,12 +14126,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN103">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
